--- a/Deliverables/BOM/Bill of Materials-John Wollam.xlsx
+++ b/Deliverables/BOM/Bill of Materials-John Wollam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B4C7CF-87BB-4372-8325-1C1108F6C6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0568FC7B-22D4-4BEF-9FF9-BDCEB090D386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="211">
   <si>
     <t>Component list</t>
   </si>
@@ -182,9 +182,6 @@
     <t>CAP TANT 100UF 20% 25V 2917</t>
   </si>
   <si>
-    <t>470uF ±20% 50V 12.5mm 13.5mm 1000hrs 105℃ -40℃~+105℃ SMD,12.5x13.5mm Aluminum Electrolytic Capacitors - SMD RoHS</t>
-  </si>
-  <si>
     <t>40V 500mV@2A 2A SMA(DO-214AC) Schottky Barrier Diodes (SBD) ROHS</t>
   </si>
   <si>
@@ -263,9 +260,6 @@
     <t>CAP- 2917</t>
   </si>
   <si>
-    <t>VT1H471MI135000CE0</t>
-  </si>
-  <si>
     <t>SMA</t>
   </si>
   <si>
@@ -377,9 +371,6 @@
     <t>Kyocera AVX</t>
   </si>
   <si>
-    <t>Changzhou Huawei Elec</t>
-  </si>
-  <si>
     <t>Yangzhou</t>
   </si>
   <si>
@@ -540,9 +531,6 @@
   </si>
   <si>
     <t>C7230</t>
-  </si>
-  <si>
-    <t>C191227</t>
   </si>
   <si>
     <t>C2886579</t>
@@ -645,9 +633,6 @@
     <t>ALiexpress</t>
   </si>
   <si>
-    <t>Alibaba</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remarks </t>
   </si>
   <si>
@@ -666,7 +651,19 @@
     <t>Total Cost Single Board</t>
   </si>
   <si>
-    <t xml:space="preserve">Quote Required from Supplier </t>
+    <t xml:space="preserve"> 470uF 7.7mm 10V 6.3mm ±20% SMD,6.3x7.7mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
+  </si>
+  <si>
+    <t>RVT1A471M0607</t>
+  </si>
+  <si>
+    <t>ROQANG</t>
+  </si>
+  <si>
+    <t>C335982</t>
+  </si>
+  <si>
+    <t>5TJ480000XYLBC</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1234,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1339,38 +1336,8 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1520,6 +1487,39 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="20" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1864,7 +1864,7 @@
     <col min="2" max="2" width="3.140625" style="23" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
     <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.42578125" customWidth="1"/>
     <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1884,9 +1884,9 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="43"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="100"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1904,13 +1904,13 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
       <c r="N2" s="33"/>
       <c r="O2" s="33"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="45"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="97"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -1934,7 +1934,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="40"/>
+      <c r="R3" s="94"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1958,7 +1958,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="41"/>
+      <c r="R4" s="95"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1982,7 +1982,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
-      <c r="R5" s="41"/>
+      <c r="R5" s="95"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2002,7 +2002,7 @@
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
-      <c r="R6" s="41"/>
+      <c r="R6" s="95"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2022,7 +2022,7 @@
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
-      <c r="R7" s="41"/>
+      <c r="R7" s="95"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2042,7 +2042,7 @@
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
-      <c r="R8" s="41"/>
+      <c r="R8" s="95"/>
     </row>
     <row r="9" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2052,86 +2052,86 @@
       <c r="C9" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="64" t="s">
+      <c r="D9" s="55" t="s">
         <v>42</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="64" t="s">
-        <v>91</v>
+        <v>73</v>
+      </c>
+      <c r="F9" s="55" t="s">
+        <v>89</v>
       </c>
       <c r="G9" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="H9" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="J9" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="L9" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="M9" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="H9" s="64" t="s">
-        <v>110</v>
-      </c>
-      <c r="I9" s="32" t="s">
+      <c r="N9" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="J9" s="64" t="s">
-        <v>132</v>
-      </c>
-      <c r="K9" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="L9" s="46" t="s">
+      <c r="O9" s="78" t="s">
         <v>156</v>
       </c>
-      <c r="M9" s="32" t="s">
+      <c r="P9" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="N9" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="O9" s="87" t="s">
-        <v>159</v>
-      </c>
-      <c r="P9" s="32" t="s">
-        <v>160</v>
-      </c>
       <c r="Q9" s="32" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="R9" s="32" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="57">
+      <c r="B10" s="48">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="65" t="s">
+      <c r="D10" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="60" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="74" t="s">
-        <v>161</v>
-      </c>
-      <c r="H10" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="I10" s="60" t="s">
-        <v>162</v>
-      </c>
-      <c r="J10" s="65" t="s">
-        <v>133</v>
-      </c>
-      <c r="K10" s="83">
+      <c r="E10" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="H10" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="I10" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="J10" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="K10" s="74">
         <v>6</v>
       </c>
-      <c r="L10" s="79">
+      <c r="L10" s="70">
         <f>K10*10</f>
         <v>60</v>
       </c>
@@ -2139,52 +2139,52 @@
         <v>100</v>
       </c>
       <c r="N10" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="O10" s="88">
+        <v>160</v>
+      </c>
+      <c r="O10" s="79">
         <v>3.3E-3</v>
       </c>
-      <c r="P10" s="92">
+      <c r="P10" s="83">
         <f>O10*M10</f>
         <v>0.33</v>
       </c>
-      <c r="Q10" s="92"/>
-      <c r="R10" s="92"/>
+      <c r="Q10" s="83"/>
+      <c r="R10" s="83"/>
     </row>
     <row r="11" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="58">
+      <c r="B11" s="49">
         <f t="shared" ref="B11:B39" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="66" t="s">
+      <c r="D11" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="66" t="s">
-        <v>93</v>
-      </c>
-      <c r="G11" s="75" t="s">
+      <c r="E11" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H11" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="I11" s="52" t="s">
         <v>161</v>
       </c>
-      <c r="H11" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="I11" s="61" t="s">
-        <v>164</v>
-      </c>
-      <c r="J11" s="66" t="s">
-        <v>134</v>
-      </c>
-      <c r="K11" s="84">
+      <c r="J11" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="K11" s="75">
         <v>2</v>
       </c>
-      <c r="L11" s="80">
+      <c r="L11" s="71">
         <f t="shared" ref="L11:L40" si="1">K11*10</f>
         <v>20</v>
       </c>
@@ -2192,52 +2192,52 @@
         <v>100</v>
       </c>
       <c r="N11" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O11" s="89">
+        <v>160</v>
+      </c>
+      <c r="O11" s="80">
         <v>3.8E-3</v>
       </c>
-      <c r="P11" s="93">
-        <f t="shared" ref="P11:R40" si="2">O11*M11</f>
+      <c r="P11" s="84">
+        <f t="shared" ref="P11:P40" si="2">O11*M11</f>
         <v>0.38</v>
       </c>
-      <c r="Q11" s="93"/>
-      <c r="R11" s="93"/>
+      <c r="Q11" s="84"/>
+      <c r="R11" s="84"/>
     </row>
     <row r="12" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="58">
+      <c r="B12" s="49">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H12" s="67" t="s">
-        <v>112</v>
-      </c>
-      <c r="I12" s="62" t="s">
-        <v>165</v>
-      </c>
-      <c r="J12" s="67" t="s">
-        <v>135</v>
-      </c>
-      <c r="K12" s="85">
+      <c r="E12" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="I12" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="J12" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="K12" s="76">
         <v>2</v>
       </c>
-      <c r="L12" s="81">
+      <c r="L12" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -2245,52 +2245,52 @@
         <v>30</v>
       </c>
       <c r="N12" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O12" s="90">
+        <v>160</v>
+      </c>
+      <c r="O12" s="81">
         <v>3.95E-2</v>
       </c>
-      <c r="P12" s="94">
+      <c r="P12" s="85">
         <f t="shared" si="2"/>
         <v>1.1850000000000001</v>
       </c>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="94"/>
+      <c r="Q12" s="85"/>
+      <c r="R12" s="85"/>
     </row>
     <row r="13" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="58">
+      <c r="B13" s="49">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="66" t="s">
+      <c r="D13" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="66" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H13" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="I13" s="61" t="s">
-        <v>166</v>
-      </c>
-      <c r="J13" s="66" t="s">
-        <v>136</v>
-      </c>
-      <c r="K13" s="84">
+      <c r="E13" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H13" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="I13" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="J13" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="K13" s="75">
         <v>1</v>
       </c>
-      <c r="L13" s="80">
+      <c r="L13" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -2298,52 +2298,52 @@
         <v>100</v>
       </c>
       <c r="N13" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O13" s="89">
+        <v>160</v>
+      </c>
+      <c r="O13" s="80">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="P13" s="93">
+      <c r="P13" s="84">
         <f t="shared" si="2"/>
         <v>0.26</v>
       </c>
-      <c r="Q13" s="93"/>
-      <c r="R13" s="93"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="84"/>
     </row>
     <row r="14" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="58">
+      <c r="B14" s="49">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="D14" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H14" s="67" t="s">
-        <v>113</v>
-      </c>
-      <c r="I14" s="62" t="s">
-        <v>167</v>
-      </c>
-      <c r="J14" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="K14" s="85">
+      <c r="E14" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="K14" s="76">
         <v>2</v>
       </c>
-      <c r="L14" s="81">
+      <c r="L14" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -2351,52 +2351,52 @@
         <v>30</v>
       </c>
       <c r="N14" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O14" s="90">
+        <v>160</v>
+      </c>
+      <c r="O14" s="81">
         <v>8.2699999999999996E-2</v>
       </c>
-      <c r="P14" s="94">
+      <c r="P14" s="85">
         <f t="shared" si="2"/>
         <v>2.4809999999999999</v>
       </c>
-      <c r="Q14" s="94"/>
-      <c r="R14" s="94"/>
+      <c r="Q14" s="85"/>
+      <c r="R14" s="85"/>
     </row>
     <row r="15" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="58">
+      <c r="B15" s="49">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="66" t="s">
+      <c r="D15" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H15" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="61" t="s">
-        <v>168</v>
-      </c>
-      <c r="J15" s="66" t="s">
-        <v>138</v>
-      </c>
-      <c r="K15" s="84">
+      <c r="E15" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="I15" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="J15" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="K15" s="75">
         <v>1</v>
       </c>
-      <c r="L15" s="80">
+      <c r="L15" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -2404,52 +2404,52 @@
         <v>100</v>
       </c>
       <c r="N15" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O15" s="89">
+        <v>160</v>
+      </c>
+      <c r="O15" s="80">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="P15" s="93">
+      <c r="P15" s="84">
         <f t="shared" si="2"/>
         <v>0.33999999999999997</v>
       </c>
-      <c r="Q15" s="93"/>
-      <c r="R15" s="93"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
     </row>
     <row r="16" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="58">
+      <c r="B16" s="49">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C16" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="62" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="67" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H16" s="67" t="s">
-        <v>114</v>
-      </c>
-      <c r="I16" s="62" t="s">
-        <v>169</v>
-      </c>
-      <c r="J16" s="67" t="s">
-        <v>139</v>
-      </c>
-      <c r="K16" s="85">
+      <c r="E16" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H16" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="J16" s="58" t="s">
+        <v>136</v>
+      </c>
+      <c r="K16" s="76">
         <v>1</v>
       </c>
-      <c r="L16" s="81">
+      <c r="L16" s="72">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -2457,52 +2457,52 @@
         <v>12</v>
       </c>
       <c r="N16" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O16" s="90">
+        <v>160</v>
+      </c>
+      <c r="O16" s="81">
         <v>1.1614</v>
       </c>
-      <c r="P16" s="94">
+      <c r="P16" s="85">
         <f t="shared" si="2"/>
         <v>13.9368</v>
       </c>
-      <c r="Q16" s="94"/>
-      <c r="R16" s="94"/>
-    </row>
-    <row r="17" spans="1:18" ht="102" x14ac:dyDescent="0.25">
+      <c r="Q16" s="85"/>
+      <c r="R16" s="85"/>
+    </row>
+    <row r="17" spans="1:18" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="58">
+      <c r="B17" s="49">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="F17" s="66" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" s="66" t="s">
-        <v>115</v>
-      </c>
-      <c r="I17" s="61" t="s">
-        <v>170</v>
-      </c>
-      <c r="J17" s="66" t="s">
-        <v>140</v>
-      </c>
-      <c r="K17" s="84">
+      <c r="D17" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" s="57" t="s">
+        <v>207</v>
+      </c>
+      <c r="G17" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="I17" s="52" t="s">
+        <v>209</v>
+      </c>
+      <c r="J17" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" s="75">
         <v>1</v>
       </c>
-      <c r="L17" s="80">
+      <c r="L17" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -2510,52 +2510,52 @@
         <v>12</v>
       </c>
       <c r="N17" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O17" s="89">
-        <v>0.34089999999999998</v>
-      </c>
-      <c r="P17" s="93">
+        <v>160</v>
+      </c>
+      <c r="O17" s="80">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="P17" s="84">
         <f t="shared" si="2"/>
-        <v>4.0907999999999998</v>
-      </c>
-      <c r="Q17" s="93"/>
-      <c r="R17" s="93"/>
+        <v>0.55080000000000007</v>
+      </c>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="84"/>
     </row>
     <row r="18" spans="1:18" ht="51" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="58">
+      <c r="B18" s="49">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="67" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="62" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="67" t="s">
-        <v>141</v>
-      </c>
-      <c r="G18" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="I18" s="62" t="s">
-        <v>171</v>
-      </c>
-      <c r="J18" s="73" t="s">
-        <v>172</v>
-      </c>
-      <c r="K18" s="85">
+      <c r="D18" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="G18" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H18" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="I18" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="J18" s="64" t="s">
+        <v>168</v>
+      </c>
+      <c r="K18" s="76">
         <v>1</v>
       </c>
-      <c r="L18" s="81">
+      <c r="L18" s="72">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -2563,52 +2563,52 @@
         <v>20</v>
       </c>
       <c r="N18" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O18" s="90">
+        <v>160</v>
+      </c>
+      <c r="O18" s="81">
         <v>3.1699999999999999E-2</v>
       </c>
-      <c r="P18" s="94">
+      <c r="P18" s="85">
         <f t="shared" si="2"/>
         <v>0.63400000000000001</v>
       </c>
-      <c r="Q18" s="94"/>
-      <c r="R18" s="94"/>
+      <c r="Q18" s="85"/>
+      <c r="R18" s="85"/>
     </row>
     <row r="19" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="58">
+      <c r="B19" s="49">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="66" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="F19" s="70" t="s">
-        <v>99</v>
-      </c>
-      <c r="G19" s="61" t="s">
-        <v>200</v>
-      </c>
-      <c r="H19" s="66" t="s">
-        <v>117</v>
-      </c>
-      <c r="I19" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="J19" s="78" t="s">
-        <v>172</v>
-      </c>
-      <c r="K19" s="84">
+      <c r="D19" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="H19" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="J19" s="69" t="s">
+        <v>168</v>
+      </c>
+      <c r="K19" s="75">
         <v>1</v>
       </c>
-      <c r="L19" s="80">
+      <c r="L19" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -2616,52 +2616,52 @@
         <v>11</v>
       </c>
       <c r="N19" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O19" s="89">
+        <v>160</v>
+      </c>
+      <c r="O19" s="80">
         <v>0.64200000000000002</v>
       </c>
-      <c r="P19" s="93">
+      <c r="P19" s="84">
         <f t="shared" si="2"/>
         <v>7.0620000000000003</v>
       </c>
-      <c r="Q19" s="93"/>
-      <c r="R19" s="93"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
     </row>
     <row r="20" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="58">
+      <c r="B20" s="49">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C20" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="67" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="F20" s="71" t="s">
-        <v>79</v>
-      </c>
-      <c r="G20" s="62" t="s">
-        <v>192</v>
-      </c>
-      <c r="H20" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="I20" s="62" t="s">
-        <v>193</v>
-      </c>
-      <c r="J20" s="73" t="s">
-        <v>172</v>
-      </c>
-      <c r="K20" s="85">
+      <c r="D20" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="H20" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="J20" s="64" t="s">
+        <v>168</v>
+      </c>
+      <c r="K20" s="76">
         <v>1</v>
       </c>
-      <c r="L20" s="81">
+      <c r="L20" s="72">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -2669,52 +2669,52 @@
         <v>15</v>
       </c>
       <c r="N20" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O20" s="90">
+        <v>160</v>
+      </c>
+      <c r="O20" s="81">
         <v>0.125</v>
       </c>
-      <c r="P20" s="94">
+      <c r="P20" s="85">
         <f t="shared" si="2"/>
         <v>1.875</v>
       </c>
-      <c r="Q20" s="94"/>
-      <c r="R20" s="94"/>
+      <c r="Q20" s="85"/>
+      <c r="R20" s="85"/>
     </row>
     <row r="21" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="58">
+      <c r="B21" s="49">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="F21" s="72" t="s">
-        <v>189</v>
-      </c>
-      <c r="G21" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="66" t="s">
-        <v>190</v>
-      </c>
-      <c r="I21" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="J21" s="78" t="s">
-        <v>172</v>
-      </c>
-      <c r="K21" s="84">
+      <c r="D21" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="G21" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H21" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="I21" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="J21" s="69" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21" s="75">
         <v>1</v>
       </c>
-      <c r="L21" s="80">
+      <c r="L21" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -2722,104 +2722,104 @@
         <v>15</v>
       </c>
       <c r="N21" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O21" s="89">
+        <v>160</v>
+      </c>
+      <c r="O21" s="80">
         <v>8.3500000000000005E-2</v>
       </c>
-      <c r="P21" s="93">
+      <c r="P21" s="84">
         <f t="shared" si="2"/>
         <v>1.2525000000000002</v>
       </c>
-      <c r="Q21" s="93"/>
-      <c r="R21" s="93"/>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="84"/>
     </row>
     <row r="22" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="58">
+      <c r="B22" s="49">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C22" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="67" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="F22" s="67" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H22" s="67" t="s">
-        <v>119</v>
-      </c>
-      <c r="I22" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="J22" s="73" t="s">
-        <v>161</v>
-      </c>
-      <c r="K22" s="85">
+      <c r="D22" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H22" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="J22" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="K22" s="76">
         <v>1</v>
       </c>
-      <c r="L22" s="81">
+      <c r="L22" s="72">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="M22" s="28" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N22" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="O22" s="91" t="s">
-        <v>161</v>
-      </c>
-      <c r="P22" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q22" s="76"/>
-      <c r="R22" s="76"/>
+        <v>158</v>
+      </c>
+      <c r="O22" s="82" t="s">
+        <v>158</v>
+      </c>
+      <c r="P22" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
     </row>
     <row r="23" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="58">
+      <c r="B23" s="49">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="66" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="F23" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="G23" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H23" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="I23" s="61" t="s">
-        <v>173</v>
-      </c>
-      <c r="J23" s="66" t="s">
-        <v>142</v>
-      </c>
-      <c r="K23" s="84">
+      <c r="D23" s="57" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H23" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="I23" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="J23" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="K23" s="75">
         <v>1</v>
       </c>
-      <c r="L23" s="80">
+      <c r="L23" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -2827,52 +2827,52 @@
         <v>15</v>
       </c>
       <c r="N23" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O23" s="89">
+        <v>160</v>
+      </c>
+      <c r="O23" s="80">
         <v>0.1799</v>
       </c>
-      <c r="P23" s="93">
+      <c r="P23" s="84">
         <f t="shared" si="2"/>
         <v>2.6985000000000001</v>
       </c>
-      <c r="Q23" s="93"/>
-      <c r="R23" s="93"/>
+      <c r="Q23" s="84"/>
+      <c r="R23" s="84"/>
     </row>
     <row r="24" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="58">
+      <c r="B24" s="49">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="67" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24" s="71">
+      <c r="D24" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="62">
         <v>61300311121</v>
       </c>
-      <c r="G24" s="62" t="s">
-        <v>194</v>
-      </c>
-      <c r="H24" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="I24" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="J24" s="73" t="s">
-        <v>175</v>
-      </c>
-      <c r="K24" s="85">
+      <c r="G24" s="53" t="s">
+        <v>190</v>
+      </c>
+      <c r="H24" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="I24" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="J24" s="64" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" s="76">
         <v>1</v>
       </c>
-      <c r="L24" s="81">
+      <c r="L24" s="72">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -2880,52 +2880,52 @@
         <v>50</v>
       </c>
       <c r="N24" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O24" s="90">
+        <v>160</v>
+      </c>
+      <c r="O24" s="81">
         <v>1.84E-2</v>
       </c>
-      <c r="P24" s="94">
+      <c r="P24" s="85">
         <f t="shared" si="2"/>
         <v>0.91999999999999993</v>
       </c>
-      <c r="Q24" s="94"/>
-      <c r="R24" s="94"/>
+      <c r="Q24" s="85"/>
+      <c r="R24" s="85"/>
     </row>
     <row r="25" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="58">
+      <c r="B25" s="49">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="66" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="61" t="s">
-        <v>83</v>
-      </c>
-      <c r="F25" s="66" t="s">
-        <v>100</v>
-      </c>
-      <c r="G25" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="66" t="s">
-        <v>122</v>
-      </c>
-      <c r="I25" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="J25" s="78" t="s">
-        <v>175</v>
-      </c>
-      <c r="K25" s="84">
+      <c r="D25" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H25" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="I25" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="J25" s="69" t="s">
+        <v>171</v>
+      </c>
+      <c r="K25" s="75">
         <v>6</v>
       </c>
-      <c r="L25" s="80">
+      <c r="L25" s="71">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
@@ -2933,52 +2933,52 @@
         <v>70</v>
       </c>
       <c r="N25" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O25" s="89">
+        <v>160</v>
+      </c>
+      <c r="O25" s="80">
         <v>0.20250000000000001</v>
       </c>
-      <c r="P25" s="93">
+      <c r="P25" s="84">
         <f t="shared" si="2"/>
         <v>14.175000000000001</v>
       </c>
-      <c r="Q25" s="93"/>
-      <c r="R25" s="93"/>
+      <c r="Q25" s="84"/>
+      <c r="R25" s="84"/>
     </row>
     <row r="26" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="58">
+      <c r="B26" s="49">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="62" t="s">
+      <c r="C26" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="71" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" s="62" t="s">
-        <v>196</v>
-      </c>
-      <c r="H26" s="67" t="s">
-        <v>123</v>
-      </c>
-      <c r="I26" s="62" t="s">
-        <v>197</v>
-      </c>
-      <c r="J26" s="67" t="s">
-        <v>143</v>
-      </c>
-      <c r="K26" s="85">
+      <c r="D26" s="58" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="H26" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="I26" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="J26" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="K26" s="76">
         <v>2</v>
       </c>
-      <c r="L26" s="81">
+      <c r="L26" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -2986,52 +2986,52 @@
         <v>25</v>
       </c>
       <c r="N26" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O26" s="90">
+        <v>160</v>
+      </c>
+      <c r="O26" s="81">
         <v>0.1135</v>
       </c>
-      <c r="P26" s="94">
+      <c r="P26" s="85">
         <f t="shared" si="2"/>
         <v>2.8374999999999999</v>
       </c>
-      <c r="Q26" s="94"/>
-      <c r="R26" s="94"/>
+      <c r="Q26" s="85"/>
+      <c r="R26" s="85"/>
     </row>
     <row r="27" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="58">
+      <c r="B27" s="49">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="66" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" s="61" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="70" t="s">
-        <v>102</v>
-      </c>
-      <c r="G27" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="H27" s="66" t="s">
-        <v>124</v>
-      </c>
-      <c r="I27" s="61" t="s">
-        <v>199</v>
-      </c>
-      <c r="J27" s="66" t="s">
-        <v>144</v>
-      </c>
-      <c r="K27" s="84">
+      <c r="D27" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="G27" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="H27" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="I27" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="J27" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="K27" s="75">
         <v>1</v>
       </c>
-      <c r="L27" s="80">
+      <c r="L27" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3039,52 +3039,52 @@
         <v>50</v>
       </c>
       <c r="N27" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O27" s="89">
+        <v>160</v>
+      </c>
+      <c r="O27" s="80">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="P27" s="93">
+      <c r="P27" s="84">
         <f t="shared" si="2"/>
         <v>0.32500000000000001</v>
       </c>
-      <c r="Q27" s="93"/>
-      <c r="R27" s="93"/>
+      <c r="Q27" s="84"/>
+      <c r="R27" s="84"/>
     </row>
     <row r="28" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="58">
+      <c r="B28" s="49">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="62" t="s">
+      <c r="C28" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="E28" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="G28" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H28" s="67" t="s">
-        <v>111</v>
-      </c>
-      <c r="I28" s="62" t="s">
-        <v>176</v>
-      </c>
-      <c r="J28" s="67" t="s">
-        <v>145</v>
-      </c>
-      <c r="K28" s="85">
+      <c r="D28" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="G28" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H28" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="I28" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="J28" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="K28" s="76">
         <v>11</v>
       </c>
-      <c r="L28" s="81">
+      <c r="L28" s="72">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
@@ -3092,52 +3092,52 @@
         <v>200</v>
       </c>
       <c r="N28" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O28" s="90">
+        <v>160</v>
+      </c>
+      <c r="O28" s="81">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="P28" s="94">
+      <c r="P28" s="85">
         <f t="shared" si="2"/>
         <v>0.32</v>
       </c>
-      <c r="Q28" s="94"/>
-      <c r="R28" s="94"/>
+      <c r="Q28" s="85"/>
+      <c r="R28" s="85"/>
     </row>
     <row r="29" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="58">
+      <c r="B29" s="49">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="G29" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H29" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="I29" s="61" t="s">
-        <v>177</v>
-      </c>
-      <c r="J29" s="66" t="s">
-        <v>146</v>
-      </c>
-      <c r="K29" s="84">
+      <c r="D29" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="F29" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="G29" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H29" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="I29" s="52" t="s">
+        <v>173</v>
+      </c>
+      <c r="J29" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="K29" s="75">
         <v>13</v>
       </c>
-      <c r="L29" s="80">
+      <c r="L29" s="71">
         <f t="shared" si="1"/>
         <v>130</v>
       </c>
@@ -3145,52 +3145,52 @@
         <v>200</v>
       </c>
       <c r="N29" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O29" s="89">
+        <v>160</v>
+      </c>
+      <c r="O29" s="80">
         <v>1.4E-3</v>
       </c>
-      <c r="P29" s="93">
+      <c r="P29" s="84">
         <f t="shared" si="2"/>
         <v>0.27999999999999997</v>
       </c>
-      <c r="Q29" s="93"/>
-      <c r="R29" s="93"/>
+      <c r="Q29" s="84"/>
+      <c r="R29" s="84"/>
     </row>
     <row r="30" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="58">
+      <c r="B30" s="49">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="62" t="s">
+      <c r="C30" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="F30" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="G30" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H30" s="67" t="s">
-        <v>111</v>
-      </c>
-      <c r="I30" s="62" t="s">
-        <v>178</v>
-      </c>
-      <c r="J30" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="K30" s="85">
+      <c r="D30" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="G30" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H30" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="I30" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="J30" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="K30" s="76">
         <v>1</v>
       </c>
-      <c r="L30" s="81">
+      <c r="L30" s="72">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3198,52 +3198,52 @@
         <v>100</v>
       </c>
       <c r="N30" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O30" s="90">
+        <v>160</v>
+      </c>
+      <c r="O30" s="81">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="P30" s="94">
+      <c r="P30" s="85">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="Q30" s="94"/>
-      <c r="R30" s="94"/>
+      <c r="Q30" s="85"/>
+      <c r="R30" s="85"/>
     </row>
     <row r="31" spans="1:18" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="58">
+      <c r="B31" s="49">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="E31" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="F31" s="66" t="s">
-        <v>179</v>
-      </c>
-      <c r="G31" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H31" s="66" t="s">
-        <v>125</v>
-      </c>
-      <c r="I31" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="J31" s="66" t="s">
-        <v>148</v>
-      </c>
-      <c r="K31" s="84">
+      <c r="D31" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="F31" s="57" t="s">
+        <v>175</v>
+      </c>
+      <c r="G31" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H31" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="I31" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="J31" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="K31" s="75">
         <v>1</v>
       </c>
-      <c r="L31" s="80">
+      <c r="L31" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3251,52 +3251,52 @@
         <v>50</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O31" s="89">
+        <v>160</v>
+      </c>
+      <c r="O31" s="80">
         <v>4.3E-3</v>
       </c>
-      <c r="P31" s="93">
+      <c r="P31" s="84">
         <f t="shared" si="2"/>
         <v>0.215</v>
       </c>
-      <c r="Q31" s="93"/>
-      <c r="R31" s="93"/>
+      <c r="Q31" s="84"/>
+      <c r="R31" s="84"/>
     </row>
     <row r="32" spans="1:18" ht="51" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="58">
+      <c r="B32" s="49">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="62" t="s">
+      <c r="C32" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="67" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="62" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32" s="67" t="s">
-        <v>106</v>
-      </c>
-      <c r="G32" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H32" s="67" t="s">
-        <v>111</v>
-      </c>
-      <c r="I32" s="62" t="s">
-        <v>181</v>
-      </c>
-      <c r="J32" s="67" t="s">
-        <v>149</v>
-      </c>
-      <c r="K32" s="85">
+      <c r="D32" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="G32" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="I32" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="J32" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="K32" s="76">
         <v>1</v>
       </c>
-      <c r="L32" s="81">
+      <c r="L32" s="72">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3304,52 +3304,52 @@
         <v>100</v>
       </c>
       <c r="N32" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O32" s="90">
+        <v>160</v>
+      </c>
+      <c r="O32" s="81">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="P32" s="94">
+      <c r="P32" s="85">
         <f t="shared" si="2"/>
         <v>0.36</v>
       </c>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="94"/>
+      <c r="Q32" s="85"/>
+      <c r="R32" s="85"/>
     </row>
     <row r="33" spans="1:21" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="58">
+      <c r="B33" s="49">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="F33" s="66" t="s">
-        <v>182</v>
-      </c>
-      <c r="G33" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H33" s="66" t="s">
-        <v>126</v>
-      </c>
-      <c r="I33" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="J33" s="66" t="s">
-        <v>150</v>
-      </c>
-      <c r="K33" s="84">
+      <c r="D33" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="F33" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="G33" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H33" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="I33" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="J33" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="K33" s="75">
         <v>1</v>
       </c>
-      <c r="L33" s="80">
+      <c r="L33" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3357,104 +3357,104 @@
         <v>100</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O33" s="89">
+        <v>160</v>
+      </c>
+      <c r="O33" s="80">
         <v>1.4E-3</v>
       </c>
-      <c r="P33" s="93">
+      <c r="P33" s="84">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="Q33" s="93"/>
-      <c r="R33" s="93"/>
+      <c r="Q33" s="84"/>
+      <c r="R33" s="84"/>
     </row>
     <row r="34" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="58">
+      <c r="B34" s="49">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="62" t="s">
+      <c r="C34" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="67" t="s">
-        <v>67</v>
-      </c>
-      <c r="E34" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="F34" s="73" t="s">
-        <v>161</v>
-      </c>
-      <c r="G34" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H34" s="73" t="s">
-        <v>161</v>
-      </c>
-      <c r="I34" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="J34" s="73" t="s">
-        <v>161</v>
-      </c>
-      <c r="K34" s="76">
+      <c r="D34" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="G34" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H34" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="I34" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="J34" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="K34" s="67">
         <v>1</v>
       </c>
-      <c r="L34" s="69">
+      <c r="L34" s="60">
         <f>K34*10</f>
         <v>10</v>
       </c>
       <c r="M34" s="28" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N34" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="O34" s="91" t="s">
-        <v>161</v>
-      </c>
-      <c r="P34" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q34" s="76"/>
-      <c r="R34" s="76"/>
+        <v>158</v>
+      </c>
+      <c r="O34" s="82" t="s">
+        <v>158</v>
+      </c>
+      <c r="P34" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q34" s="67"/>
+      <c r="R34" s="67"/>
     </row>
     <row r="35" spans="1:21" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="58">
+      <c r="B35" s="49">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="61" t="s">
+      <c r="C35" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="66" t="s">
-        <v>68</v>
-      </c>
-      <c r="E35" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="F35" s="66" t="s">
-        <v>107</v>
-      </c>
-      <c r="G35" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H35" s="66" t="s">
-        <v>127</v>
-      </c>
-      <c r="I35" s="61" t="s">
-        <v>184</v>
-      </c>
-      <c r="J35" s="78" t="s">
-        <v>161</v>
-      </c>
-      <c r="K35" s="84">
+      <c r="D35" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="F35" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="G35" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H35" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="I35" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="J35" s="69" t="s">
+        <v>158</v>
+      </c>
+      <c r="K35" s="75">
         <v>1</v>
       </c>
-      <c r="L35" s="80">
+      <c r="L35" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3462,52 +3462,52 @@
         <v>12</v>
       </c>
       <c r="N35" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O35" s="89">
+        <v>160</v>
+      </c>
+      <c r="O35" s="80">
         <v>0.45090000000000002</v>
       </c>
-      <c r="P35" s="93">
+      <c r="P35" s="84">
         <f t="shared" si="2"/>
         <v>5.4108000000000001</v>
       </c>
-      <c r="Q35" s="93"/>
-      <c r="R35" s="93"/>
+      <c r="Q35" s="84"/>
+      <c r="R35" s="84"/>
     </row>
     <row r="36" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="58">
+      <c r="B36" s="49">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="62" t="s">
+      <c r="C36" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="E36" s="62" t="s">
-        <v>202</v>
-      </c>
-      <c r="F36" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="G36" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H36" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="I36" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="J36" s="73" t="s">
-        <v>161</v>
-      </c>
-      <c r="K36" s="85">
+      <c r="D36" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="F36" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="G36" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H36" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="I36" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="J36" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="K36" s="76">
         <v>1</v>
       </c>
-      <c r="L36" s="81">
+      <c r="L36" s="72">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3515,55 +3515,55 @@
         <v>11</v>
       </c>
       <c r="N36" s="39" t="s">
-        <v>203</v>
-      </c>
-      <c r="O36" s="90">
+        <v>199</v>
+      </c>
+      <c r="O36" s="81">
         <v>6.5</v>
       </c>
-      <c r="P36" s="94">
+      <c r="P36" s="85">
         <f t="shared" si="2"/>
         <v>71.5</v>
       </c>
-      <c r="Q36" s="94"/>
-      <c r="R36" s="94"/>
+      <c r="Q36" s="85"/>
+      <c r="R36" s="85"/>
       <c r="U36">
         <v>3.16</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="58">
+      <c r="B37" s="49">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="66" t="s">
-        <v>70</v>
-      </c>
-      <c r="E37" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37" s="66" t="s">
-        <v>109</v>
-      </c>
-      <c r="G37" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H37" s="66" t="s">
-        <v>129</v>
-      </c>
-      <c r="I37" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="J37" s="78" t="s">
-        <v>161</v>
-      </c>
-      <c r="K37" s="84">
+      <c r="D37" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="G37" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H37" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="I37" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="J37" s="69" t="s">
+        <v>158</v>
+      </c>
+      <c r="K37" s="75">
         <v>1</v>
       </c>
-      <c r="L37" s="80">
+      <c r="L37" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3571,52 +3571,52 @@
         <v>11</v>
       </c>
       <c r="N37" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O37" s="89">
+        <v>160</v>
+      </c>
+      <c r="O37" s="80">
         <v>0.39679999999999999</v>
       </c>
-      <c r="P37" s="93">
+      <c r="P37" s="84">
         <f t="shared" si="2"/>
         <v>4.3647999999999998</v>
       </c>
-      <c r="Q37" s="93"/>
-      <c r="R37" s="93"/>
+      <c r="Q37" s="84"/>
+      <c r="R37" s="84"/>
     </row>
     <row r="38" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="58">
+      <c r="B38" s="49">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="62" t="s">
+      <c r="C38" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="E38" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="F38" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="G38" s="76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H38" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="I38" s="62" t="s">
-        <v>187</v>
-      </c>
-      <c r="J38" s="73" t="s">
-        <v>161</v>
-      </c>
-      <c r="K38" s="85">
+      <c r="D38" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="F38" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="G38" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="H38" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="I38" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="J38" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="K38" s="76">
         <v>1</v>
       </c>
-      <c r="L38" s="81">
+      <c r="L38" s="72">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3624,52 +3624,52 @@
         <v>11</v>
       </c>
       <c r="N38" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="O38" s="90">
+        <v>160</v>
+      </c>
+      <c r="O38" s="81">
         <v>0.8458</v>
       </c>
-      <c r="P38" s="94">
+      <c r="P38" s="85">
         <f t="shared" si="2"/>
         <v>9.3038000000000007</v>
       </c>
-      <c r="Q38" s="94"/>
-      <c r="R38" s="94"/>
+      <c r="Q38" s="85"/>
+      <c r="R38" s="85"/>
     </row>
     <row r="39" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="58">
+      <c r="B39" s="49">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="D39" s="66" t="s">
-        <v>72</v>
-      </c>
-      <c r="E39" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="F39" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="G39" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="H39" s="66" t="s">
-        <v>130</v>
-      </c>
-      <c r="I39" s="61" t="s">
-        <v>188</v>
-      </c>
-      <c r="J39" s="78" t="s">
-        <v>161</v>
-      </c>
-      <c r="K39" s="84">
+      <c r="D39" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="F39" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="H39" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="I39" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="J39" s="69" t="s">
+        <v>158</v>
+      </c>
+      <c r="K39" s="75">
         <v>1</v>
       </c>
-      <c r="L39" s="80">
+      <c r="L39" s="71">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3677,52 +3677,52 @@
         <v>11</v>
       </c>
       <c r="N39" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="O39" s="89">
+        <v>160</v>
+      </c>
+      <c r="O39" s="80">
         <v>0.2336</v>
       </c>
-      <c r="P39" s="93">
+      <c r="P39" s="84">
         <f t="shared" si="2"/>
         <v>2.5695999999999999</v>
       </c>
-      <c r="Q39" s="93"/>
-      <c r="R39" s="93"/>
+      <c r="Q39" s="84"/>
+      <c r="R39" s="84"/>
     </row>
     <row r="40" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="59">
+      <c r="B40" s="50">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="63" t="s">
+      <c r="C40" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="D40" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="F40" s="68" t="s">
-        <v>90</v>
-      </c>
-      <c r="G40" s="77" t="s">
-        <v>161</v>
-      </c>
-      <c r="H40" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="I40" s="77" t="s">
-        <v>161</v>
-      </c>
-      <c r="J40" s="68" t="s">
-        <v>151</v>
-      </c>
-      <c r="K40" s="86">
+      <c r="D40" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" s="101" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" s="68" t="s">
+        <v>210</v>
+      </c>
+      <c r="H40" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="I40" s="68" t="s">
+        <v>158</v>
+      </c>
+      <c r="J40" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="K40" s="77">
         <v>1</v>
       </c>
-      <c r="L40" s="82">
+      <c r="L40" s="73">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3730,44 +3730,44 @@
         <v>11</v>
       </c>
       <c r="N40" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="O40" s="90"/>
-      <c r="P40" s="94">
+        <v>160</v>
+      </c>
+      <c r="O40" s="81">
+        <v>0.22639999999999999</v>
+      </c>
+      <c r="P40" s="85">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="100" t="s">
-        <v>211</v>
-      </c>
-      <c r="R40" s="94"/>
+        <v>2.4903999999999997</v>
+      </c>
+      <c r="Q40" s="91"/>
+      <c r="R40" s="85"/>
     </row>
     <row r="41" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="51" t="s">
+      <c r="B41" s="41"/>
+      <c r="C41" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="52"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="48" t="s">
-        <v>207</v>
-      </c>
-      <c r="N41" s="48"/>
-      <c r="O41" s="48"/>
-      <c r="P41" s="95">
+      <c r="D41" s="43"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="45"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="46"/>
+      <c r="M41" s="93" t="s">
+        <v>202</v>
+      </c>
+      <c r="N41" s="93"/>
+      <c r="O41" s="93"/>
+      <c r="P41" s="86">
         <f>SUM(P10:P40)</f>
-        <v>149.40710000000001</v>
-      </c>
-      <c r="Q41" s="97"/>
-      <c r="R41" s="97"/>
+        <v>148.35750000000002</v>
+      </c>
+      <c r="Q41" s="88"/>
+      <c r="R41" s="88"/>
     </row>
     <row r="42" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
@@ -3783,54 +3783,54 @@
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
-      <c r="L42" s="56"/>
-      <c r="M42" s="49" t="s">
-        <v>208</v>
-      </c>
-      <c r="N42" s="49"/>
-      <c r="O42" s="49"/>
-      <c r="P42" s="95">
+      <c r="L42" s="47"/>
+      <c r="M42" s="98" t="s">
+        <v>203</v>
+      </c>
+      <c r="N42" s="98"/>
+      <c r="O42" s="98"/>
+      <c r="P42" s="86">
         <f>P41/10</f>
-        <v>14.940710000000001</v>
-      </c>
-      <c r="Q42" s="98"/>
-      <c r="R42" s="98"/>
+        <v>14.835750000000001</v>
+      </c>
+      <c r="Q42" s="89"/>
+      <c r="R42" s="89"/>
     </row>
     <row r="43" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M43" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="N43" s="48"/>
-      <c r="O43" s="48"/>
-      <c r="P43" s="95">
+      <c r="M43" s="92" t="s">
+        <v>204</v>
+      </c>
+      <c r="N43" s="93"/>
+      <c r="O43" s="93"/>
+      <c r="P43" s="86">
         <v>3.16</v>
       </c>
-      <c r="Q43" s="98"/>
-      <c r="R43" s="98"/>
+      <c r="Q43" s="89"/>
+      <c r="R43" s="89"/>
     </row>
     <row r="44" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M44" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="N44" s="48"/>
-      <c r="O44" s="48"/>
-      <c r="P44" s="96">
+      <c r="M44" s="92" t="s">
+        <v>205</v>
+      </c>
+      <c r="N44" s="93"/>
+      <c r="O44" s="93"/>
+      <c r="P44" s="87">
         <f>SUM(P42:P43)</f>
-        <v>18.100709999999999</v>
-      </c>
-      <c r="Q44" s="99"/>
-      <c r="R44" s="99"/>
+        <v>17.995750000000001</v>
+      </c>
+      <c r="Q44" s="90"/>
+      <c r="R44" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="L2:M2"/>
     <mergeCell ref="M44:O44"/>
     <mergeCell ref="R3:R8"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="M41:O41"/>
     <mergeCell ref="M42:O42"/>
     <mergeCell ref="M43:O43"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="L2:M2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N10" r:id="rId1" xr:uid="{D40B14C7-1C56-4DA6-B8AA-C5629A2D0181}"/>
@@ -3840,28 +3840,28 @@
     <hyperlink ref="N14" r:id="rId5" xr:uid="{5D97E4CD-902B-46A2-9B3B-B15DB6820C8C}"/>
     <hyperlink ref="N15" r:id="rId6" xr:uid="{2E775539-906B-4179-89F8-DE620B7E5B40}"/>
     <hyperlink ref="N16" r:id="rId7" xr:uid="{4F5A2672-2E29-4022-B999-07225DE51A94}"/>
-    <hyperlink ref="N17" r:id="rId8" xr:uid="{8EA9EA9A-E9C6-4B06-B552-D62191A2C65C}"/>
-    <hyperlink ref="N18" r:id="rId9" xr:uid="{B662F39D-A233-448A-825B-1DB506E1FB5D}"/>
-    <hyperlink ref="N23" r:id="rId10" xr:uid="{6E039F18-AFCA-4A29-92EC-785BEEFD9EA6}"/>
-    <hyperlink ref="N25" r:id="rId11" xr:uid="{0A0BD431-8895-4A11-992F-B2F295C32C93}"/>
-    <hyperlink ref="N28" r:id="rId12" xr:uid="{B608BFA5-3DA0-4ABE-BF24-8B3433741BD2}"/>
-    <hyperlink ref="N29" r:id="rId13" xr:uid="{5C888BF9-266F-4B24-B07D-ED2866926086}"/>
-    <hyperlink ref="N30" r:id="rId14" xr:uid="{70962410-828C-4B23-97D4-96B8763784FF}"/>
-    <hyperlink ref="N31" r:id="rId15" xr:uid="{F8395AC9-9341-42F7-92D2-35F4E4D5FDA0}"/>
-    <hyperlink ref="N32" r:id="rId16" xr:uid="{797BDEF1-E06B-4EDB-954C-039D2F85C1A1}"/>
-    <hyperlink ref="N33" r:id="rId17" xr:uid="{AF1FCEF7-4D2D-4F32-96FE-69FBCC8BD2F7}"/>
-    <hyperlink ref="N35" r:id="rId18" xr:uid="{8DE90BC3-A79B-4461-9C1B-6C15840346EB}"/>
-    <hyperlink ref="N37" r:id="rId19" xr:uid="{F2FED3FF-375F-494E-B9B7-D48AED7C2F8A}"/>
-    <hyperlink ref="N38" r:id="rId20" xr:uid="{FDECF396-A243-431B-BE9C-184B9C62F71F}"/>
-    <hyperlink ref="N39" r:id="rId21" xr:uid="{3DCD7192-D4A4-4355-AE14-169E6DF9231F}"/>
-    <hyperlink ref="N21" r:id="rId22" xr:uid="{52A7D1B2-440E-4453-9E99-3D13C1743003}"/>
-    <hyperlink ref="N20" r:id="rId23" xr:uid="{2CE31419-5C69-4837-BA05-2DFCF3CFD556}"/>
-    <hyperlink ref="N24" r:id="rId24" xr:uid="{6D1D9E0D-337C-4A16-9971-616C5396C3D3}"/>
-    <hyperlink ref="N26" r:id="rId25" xr:uid="{55DD85C1-58E5-4C9F-9AC9-5EC55A848B4D}"/>
-    <hyperlink ref="N27" r:id="rId26" xr:uid="{B84E24E3-B019-4431-BE23-3E81EFD964D3}"/>
-    <hyperlink ref="N19" r:id="rId27" xr:uid="{13475D7A-3A1C-4BA0-AF26-5D65B57DD1B1}"/>
-    <hyperlink ref="N36" r:id="rId28" xr:uid="{0485072C-3830-4C7C-AC40-BFF0596D533E}"/>
-    <hyperlink ref="N40" r:id="rId29" xr:uid="{38BA5D02-0E2E-4541-80F2-6087250EC2DE}"/>
+    <hyperlink ref="N18" r:id="rId8" xr:uid="{B662F39D-A233-448A-825B-1DB506E1FB5D}"/>
+    <hyperlink ref="N23" r:id="rId9" xr:uid="{6E039F18-AFCA-4A29-92EC-785BEEFD9EA6}"/>
+    <hyperlink ref="N25" r:id="rId10" xr:uid="{0A0BD431-8895-4A11-992F-B2F295C32C93}"/>
+    <hyperlink ref="N28" r:id="rId11" xr:uid="{B608BFA5-3DA0-4ABE-BF24-8B3433741BD2}"/>
+    <hyperlink ref="N29" r:id="rId12" xr:uid="{5C888BF9-266F-4B24-B07D-ED2866926086}"/>
+    <hyperlink ref="N30" r:id="rId13" xr:uid="{70962410-828C-4B23-97D4-96B8763784FF}"/>
+    <hyperlink ref="N31" r:id="rId14" xr:uid="{F8395AC9-9341-42F7-92D2-35F4E4D5FDA0}"/>
+    <hyperlink ref="N32" r:id="rId15" xr:uid="{797BDEF1-E06B-4EDB-954C-039D2F85C1A1}"/>
+    <hyperlink ref="N33" r:id="rId16" xr:uid="{AF1FCEF7-4D2D-4F32-96FE-69FBCC8BD2F7}"/>
+    <hyperlink ref="N35" r:id="rId17" xr:uid="{8DE90BC3-A79B-4461-9C1B-6C15840346EB}"/>
+    <hyperlink ref="N37" r:id="rId18" xr:uid="{F2FED3FF-375F-494E-B9B7-D48AED7C2F8A}"/>
+    <hyperlink ref="N38" r:id="rId19" xr:uid="{FDECF396-A243-431B-BE9C-184B9C62F71F}"/>
+    <hyperlink ref="N39" r:id="rId20" xr:uid="{3DCD7192-D4A4-4355-AE14-169E6DF9231F}"/>
+    <hyperlink ref="N21" r:id="rId21" xr:uid="{52A7D1B2-440E-4453-9E99-3D13C1743003}"/>
+    <hyperlink ref="N20" r:id="rId22" xr:uid="{2CE31419-5C69-4837-BA05-2DFCF3CFD556}"/>
+    <hyperlink ref="N24" r:id="rId23" xr:uid="{6D1D9E0D-337C-4A16-9971-616C5396C3D3}"/>
+    <hyperlink ref="N26" r:id="rId24" xr:uid="{55DD85C1-58E5-4C9F-9AC9-5EC55A848B4D}"/>
+    <hyperlink ref="N27" r:id="rId25" xr:uid="{B84E24E3-B019-4431-BE23-3E81EFD964D3}"/>
+    <hyperlink ref="N19" r:id="rId26" xr:uid="{13475D7A-3A1C-4BA0-AF26-5D65B57DD1B1}"/>
+    <hyperlink ref="N36" r:id="rId27" xr:uid="{0485072C-3830-4C7C-AC40-BFF0596D533E}"/>
+    <hyperlink ref="N17" r:id="rId28" xr:uid="{23B04B83-DB52-4B14-810B-F39405B68FBC}"/>
+    <hyperlink ref="N40" r:id="rId29" xr:uid="{6E69C002-2834-44C3-81A7-66E9B4F73185}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
